--- a/labs/lab-05-analyse-variances-and-build-a-dashboard-with-copilot/northstar-fpa-dashboard-solution.xlsx
+++ b/labs/lab-05-analyse-variances-and-build-a-dashboard-with-copilot/northstar-fpa-dashboard-solution.xlsx
@@ -26,7 +26,7 @@
     <t>Course</t>
   </si>
   <si>
-    <t>Generative AI for Finance and Fintech (TGS-2026065050)</t>
+    <t>Microsoft Copilot for Finance (TGS-2026065050)</t>
   </si>
   <si>
     <t>TSC mapping</t>
